--- a/result/glucose_transportor_classification.xlsx
+++ b/result/glucose_transportor_classification.xlsx
@@ -1,40 +1,192 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10520"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/xluhon/Documents/GitHub/De-nevo-protein-3D-structure-yeast/result/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68069971-980E-7B41-9791-24E332618656}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView activeTab="0" autoFilterDateGrouping="1" firstSheet="0" minimized="0" showHorizontalScroll="1" showSheetTabs="1" showVerticalScroll="1" tabRatio="600" visibility="visible"/>
+    <workbookView xWindow="11240" yWindow="2640" windowWidth="26880" windowHeight="15220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="43">
+  <si>
+    <t>id</t>
+  </si>
+  <si>
+    <t>gene</t>
+  </si>
+  <si>
+    <t>number</t>
+  </si>
+  <si>
+    <t>AF-P0CD99-F1-model_v1.pdb</t>
+  </si>
+  <si>
+    <t>YDL247W</t>
+  </si>
+  <si>
+    <t>AF-Q04162-F1-model_v1.pdb</t>
+  </si>
+  <si>
+    <t>YDR387C</t>
+  </si>
+  <si>
+    <t>AF-P54854-F1-model_v1.pdb</t>
+  </si>
+  <si>
+    <t>YDL245C</t>
+  </si>
+  <si>
+    <t>AF-P13181-F1-model_v1.pdb</t>
+  </si>
+  <si>
+    <t>YLR081W</t>
+  </si>
+  <si>
+    <t>AF-P32465-F1-model_v1.pdb</t>
+  </si>
+  <si>
+    <t>YHR094C</t>
+  </si>
+  <si>
+    <t>AF-P43581-F1-model_v1.pdb</t>
+  </si>
+  <si>
+    <t>YFL011W</t>
+  </si>
+  <si>
+    <t>AF-P47185-F1-model_v1.pdb</t>
+  </si>
+  <si>
+    <t>YJR158W</t>
+  </si>
+  <si>
+    <t>AF-P53631-F1-model_v1.pdb</t>
+  </si>
+  <si>
+    <t>YNR072W</t>
+  </si>
+  <si>
+    <t>AF-P40885-F1-model_v1.pdb</t>
+  </si>
+  <si>
+    <t>YJL219W</t>
+  </si>
+  <si>
+    <t>AF-P39003-F1-model_v1.pdb</t>
+  </si>
+  <si>
+    <t>YDR343C</t>
+  </si>
+  <si>
+    <t>AF-P23585-F1-model_v1.pdb</t>
+  </si>
+  <si>
+    <t>YMR011W</t>
+  </si>
+  <si>
+    <t>AF-P32466-F1-model_v1.pdb</t>
+  </si>
+  <si>
+    <t>YDR345C</t>
+  </si>
+  <si>
+    <t>AF-P54862-F1-model_v1.pdb</t>
+  </si>
+  <si>
+    <t>YOL156W</t>
+  </si>
+  <si>
+    <t>AF-P39004-F1-model_v1.pdb</t>
+  </si>
+  <si>
+    <t>YDR342C</t>
+  </si>
+  <si>
+    <t>AF-P38695-F1-model_v1.pdb</t>
+  </si>
+  <si>
+    <t>YHR096C</t>
+  </si>
+  <si>
+    <t>AF-P39932-F1-model_v1.pdb</t>
+  </si>
+  <si>
+    <t>YDR536W</t>
+  </si>
+  <si>
+    <t>AF-P39924-F1-model_v1.pdb</t>
+  </si>
+  <si>
+    <t>YEL069C</t>
+  </si>
+  <si>
+    <t>AF-P0CE00-F1-model_v1.pdb</t>
+  </si>
+  <si>
+    <t>YJR160C</t>
+  </si>
+  <si>
+    <t>AF-P40886-F1-model_v1.pdb</t>
+  </si>
+  <si>
+    <t>YJL214W</t>
+  </si>
+  <si>
+    <t>AF-P32467-F1-model_v1.pdb</t>
+  </si>
+  <si>
+    <t>YHR092C</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b val="1"/>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -46,93 +198,48 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="1" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+  <cellXfs count="5">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle builtinId="0" hidden="0" name="Normal" xfId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium9"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -420,392 +527,309 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D21"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:F21"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="2" max="2" width="27.1640625" customWidth="1"/>
+    <col min="3" max="3" width="36.6640625" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>gene</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>number</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="1" t="n">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A2" s="1">
         <v>740</v>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>AF-P0CD99-F1-model_v1.pdb</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>YDL247W</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
+      <c r="B2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2">
         <v>0</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="1" t="n">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A3" s="1">
         <v>818</v>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>AF-Q04162-F1-model_v1.pdb</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>YDR387C</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
+      <c r="B3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D3">
         <v>1</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="1" t="n">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A4" s="1">
         <v>1095</v>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>AF-P54854-F1-model_v1.pdb</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>YDL245C</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
+      <c r="B4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D4">
         <v>2</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="1" t="n">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A5" s="1">
         <v>1108</v>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>AF-P13181-F1-model_v1.pdb</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>YLR081W</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
+      <c r="B5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D5">
         <v>3</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="1" t="n">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A6" s="1">
         <v>1160</v>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>AF-P32465-F1-model_v1.pdb</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>YHR094C</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
+      <c r="B6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D6">
         <v>4</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="1" t="n">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A7" s="1">
         <v>1405</v>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>AF-P43581-F1-model_v1.pdb</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>YFL011W</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
+      <c r="B7" t="s">
+        <v>13</v>
+      </c>
+      <c r="C7" t="s">
+        <v>14</v>
+      </c>
+      <c r="D7">
         <v>5</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="1" t="n">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A8" s="1">
         <v>1440</v>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>AF-P47185-F1-model_v1.pdb</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>YJR158W</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
+      <c r="B8" t="s">
+        <v>15</v>
+      </c>
+      <c r="C8" t="s">
+        <v>16</v>
+      </c>
+      <c r="D8">
         <v>6</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="1" t="n">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A9" s="1">
         <v>1632</v>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>AF-P53631-F1-model_v1.pdb</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>YNR072W</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
+      <c r="B9" t="s">
+        <v>17</v>
+      </c>
+      <c r="C9" t="s">
+        <v>18</v>
+      </c>
+      <c r="D9">
         <v>7</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="1" t="n">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A10" s="1">
         <v>2054</v>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>AF-P40885-F1-model_v1.pdb</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>YJL219W</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
+      <c r="B10" t="s">
+        <v>19</v>
+      </c>
+      <c r="C10" t="s">
+        <v>20</v>
+      </c>
+      <c r="D10">
         <v>8</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="1" t="n">
+    <row r="11" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="3">
         <v>3259</v>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>AF-P39003-F1-model_v1.pdb</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>YDR343C</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
+      <c r="B11" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D11" s="2">
         <v>9</v>
       </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="F11" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="3">
         <v>3500</v>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>AF-P23585-F1-model_v1.pdb</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>YMR011W</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
+      <c r="B12" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D12" s="2">
         <v>10</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="1" t="n">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A13" s="1">
         <v>3721</v>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>AF-P32466-F1-model_v1.pdb</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>YDR345C</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
+      <c r="B13" t="s">
+        <v>25</v>
+      </c>
+      <c r="C13" t="s">
+        <v>26</v>
+      </c>
+      <c r="D13">
         <v>11</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="1" t="n">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A14" s="1">
         <v>3932</v>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>AF-P54862-F1-model_v1.pdb</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>YOL156W</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
+      <c r="B14" t="s">
+        <v>27</v>
+      </c>
+      <c r="C14" t="s">
+        <v>28</v>
+      </c>
+      <c r="D14">
         <v>12</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="1" t="n">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A15" s="3">
         <v>4357</v>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>AF-P39004-F1-model_v1.pdb</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>YDR342C</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
+      <c r="B15" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="D15" s="2">
         <v>13</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="1" t="n">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A16" s="1">
         <v>4548</v>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>AF-P38695-F1-model_v1.pdb</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>YHR096C</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
+      <c r="B16" t="s">
+        <v>31</v>
+      </c>
+      <c r="C16" t="s">
+        <v>32</v>
+      </c>
+      <c r="D16">
         <v>14</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="1" t="n">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A17" s="1">
         <v>4791</v>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>AF-P39932-F1-model_v1.pdb</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>YDR536W</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
+      <c r="B17" t="s">
+        <v>33</v>
+      </c>
+      <c r="C17" t="s">
+        <v>34</v>
+      </c>
+      <c r="D17">
         <v>15</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="1" t="n">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A18" s="1">
         <v>5270</v>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>AF-P39924-F1-model_v1.pdb</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>YEL069C</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
+      <c r="B18" t="s">
+        <v>35</v>
+      </c>
+      <c r="C18" t="s">
+        <v>36</v>
+      </c>
+      <c r="D18">
         <v>16</v>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="1" t="n">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A19" s="1">
         <v>5840</v>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>AF-P0CE00-F1-model_v1.pdb</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>YJR160C</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
+      <c r="B19" t="s">
+        <v>37</v>
+      </c>
+      <c r="C19" t="s">
+        <v>38</v>
+      </c>
+      <c r="D19">
         <v>17</v>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="1" t="n">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A20" s="1">
         <v>5877</v>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>AF-P40886-F1-model_v1.pdb</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>YJL214W</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
+      <c r="B20" t="s">
+        <v>39</v>
+      </c>
+      <c r="C20" t="s">
+        <v>40</v>
+      </c>
+      <c r="D20">
         <v>18</v>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="1" t="n">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A21" s="3">
         <v>5897</v>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>AF-P32467-F1-model_v1.pdb</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>YHR092C</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
+      <c r="B21" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D21" s="2">
         <v>19</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>